--- a/dataHQ_template.xlsx
+++ b/dataHQ_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e8f29e5c69611e4f/Jephin/CODEBOOK/dataHQ PH2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{ED923E39-6290-41D0-9134-F53FC29FCF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BEECB69-25E6-4B7B-BE27-760A24A59C4D}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{ED923E39-6290-41D0-9134-F53FC29FCF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34F3F029-C531-4131-9D86-694AF489F486}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{74DC5B4E-C759-4CAF-A571-81B2E018D03A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
   <si>
     <t>India</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>editable</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -988,6 +991,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1014,9 +1020,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1068,6 +1071,10 @@
 </file>
 
 <file path=xl/persons/person1.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person2.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -1382,7 +1389,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1393,7 +1400,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="79"/>
+      <c r="A2" s="80"/>
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1402,7 +1409,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="79"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
@@ -1411,7 +1418,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="81" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="16" t="s">
@@ -1422,7 +1429,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="80"/>
+      <c r="A5" s="81"/>
       <c r="B5" s="16" t="s">
         <v>14</v>
       </c>
@@ -1431,7 +1438,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="80"/>
+      <c r="A6" s="81"/>
       <c r="B6" s="16" t="s">
         <v>16</v>
       </c>
@@ -1440,43 +1447,43 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="80"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="68">
-        <v>0</v>
+      <c r="C7" s="68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="80"/>
+      <c r="A8" s="81"/>
       <c r="B8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="68">
-        <v>0</v>
+      <c r="C8" s="68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="80"/>
+      <c r="A9" s="81"/>
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="68">
-        <v>0</v>
+      <c r="C9" s="68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="80"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="68">
-        <v>0</v>
+      <c r="C10" s="68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="80"/>
+      <c r="A11" s="81"/>
       <c r="B11" s="16" t="s">
         <v>26</v>
       </c>
@@ -1485,7 +1492,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="80"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="16" t="s">
         <v>27</v>
       </c>
@@ -1494,7 +1501,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="80"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="16" t="s">
         <v>29</v>
       </c>
@@ -1503,7 +1510,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="80"/>
+      <c r="A14" s="81"/>
       <c r="B14" s="16" t="s">
         <v>30</v>
       </c>
@@ -1512,7 +1519,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="80"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="16" t="s">
         <v>31</v>
       </c>
@@ -1521,7 +1528,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" s="31" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="80"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="30" t="s">
         <v>35</v>
       </c>
@@ -1530,7 +1537,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="81"/>
       <c r="B17" s="32" t="s">
         <v>36</v>
       </c>
@@ -1539,7 +1546,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="80"/>
+      <c r="A18" s="81"/>
       <c r="B18" s="32" t="s">
         <v>37</v>
       </c>
@@ -1548,7 +1555,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="80"/>
+      <c r="A19" s="81"/>
       <c r="B19" s="32" t="s">
         <v>38</v>
       </c>
@@ -1557,43 +1564,43 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="80"/>
+      <c r="A20" s="81"/>
       <c r="B20" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="68">
-        <v>0</v>
+      <c r="C20" s="68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="80"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="68">
-        <v>0</v>
+      <c r="C21" s="68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="80"/>
+      <c r="A22" s="81"/>
       <c r="B22" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="68">
-        <v>0</v>
+      <c r="C22" s="68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="80"/>
+      <c r="A23" s="81"/>
       <c r="B23" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="68">
-        <v>0</v>
+      <c r="C23" s="68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="80"/>
+      <c r="A24" s="81"/>
       <c r="B24" s="38" t="s">
         <v>44</v>
       </c>
@@ -1602,7 +1609,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="81" t="s">
+      <c r="A25" s="82" t="s">
         <v>46</v>
       </c>
       <c r="B25" s="40" t="s">
@@ -1613,7 +1620,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="81"/>
+      <c r="A26" s="82"/>
       <c r="B26" s="32" t="s">
         <v>49</v>
       </c>
@@ -1622,7 +1629,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="81"/>
+      <c r="A27" s="82"/>
       <c r="B27" s="32" t="s">
         <v>51</v>
       </c>
@@ -1631,7 +1638,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="81"/>
+      <c r="A28" s="82"/>
       <c r="B28" s="38" t="s">
         <v>52</v>
       </c>
@@ -1640,7 +1647,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="77" t="s">
+      <c r="A29" s="78" t="s">
         <v>53</v>
       </c>
       <c r="B29" s="40" t="s">
@@ -1651,7 +1658,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="77"/>
+      <c r="A30" s="78"/>
       <c r="B30" s="38" t="s">
         <v>56</v>
       </c>
@@ -1660,7 +1667,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="79" t="s">
         <v>58</v>
       </c>
       <c r="B31" s="32" t="s">
@@ -1671,7 +1678,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="78"/>
+      <c r="A32" s="79"/>
       <c r="B32" s="32" t="s">
         <v>60</v>
       </c>
@@ -1680,7 +1687,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="78"/>
+      <c r="A33" s="79"/>
       <c r="B33" s="32" t="s">
         <v>62</v>
       </c>
@@ -1689,7 +1696,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="78"/>
+      <c r="A34" s="79"/>
       <c r="B34" s="32" t="s">
         <v>64</v>
       </c>
@@ -1698,7 +1705,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="78"/>
+      <c r="A35" s="79"/>
       <c r="B35" s="32" t="s">
         <v>65</v>
       </c>
@@ -1707,7 +1714,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="78"/>
+      <c r="A36" s="79"/>
       <c r="B36" s="32" t="s">
         <v>67</v>
       </c>
@@ -1716,7 +1723,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="78"/>
+      <c r="A37" s="79"/>
       <c r="B37" s="38" t="s">
         <v>68</v>
       </c>
@@ -1805,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="15"/>
-      <c r="H4" s="86" t="s">
+      <c r="H4" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1828,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="15"/>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1858,12 +1865,12 @@
       <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="82">
+      <c r="D7" s="83">
         <f>D6+E6+F6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1874,11 +1881,11 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
       <c r="G8" s="15"/>
-      <c r="H8" s="86" t="s">
+      <c r="H8" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1888,12 +1895,12 @@
       <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="82">
+      <c r="D9" s="83">
         <f>D7-D8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1960,7 +1967,7 @@
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="56"/>
-      <c r="F16" s="86" t="s">
+      <c r="F16" s="77" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="3"/>
@@ -1972,7 +1979,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="56"/>
-      <c r="F17" s="86" t="s">
+      <c r="F17" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1983,7 +1990,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="60"/>
-      <c r="F18" s="86" t="s">
+      <c r="F18" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1995,7 +2002,7 @@
     </row>
     <row r="21" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="85" t="s">
         <v>41</v>
       </c>
       <c r="D21" s="33"/>
@@ -2004,7 +2011,7 @@
     </row>
     <row r="22" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
-      <c r="C22" s="85"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="35" t="s">
         <v>2</v>
       </c>
@@ -2030,7 +2037,7 @@
       <c r="D24" s="61"/>
       <c r="E24" s="61"/>
       <c r="F24" s="62"/>
-      <c r="G24" s="86" t="s">
+      <c r="G24" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2042,7 +2049,7 @@
       <c r="D25" s="63"/>
       <c r="E25" s="63"/>
       <c r="F25" s="64"/>
-      <c r="G25" s="86" t="s">
+      <c r="G25" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2054,7 +2061,7 @@
       <c r="D26" s="63"/>
       <c r="E26" s="63"/>
       <c r="F26" s="64"/>
-      <c r="G26" s="86" t="s">
+      <c r="G26" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2080,7 +2087,7 @@
       <c r="D29" s="63"/>
       <c r="E29" s="63"/>
       <c r="F29" s="64"/>
-      <c r="G29" s="86" t="s">
+      <c r="G29" s="77" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2114,7 +2121,7 @@
       <c r="D32" s="63"/>
       <c r="E32" s="63"/>
       <c r="F32" s="64"/>
-      <c r="G32" s="86" t="s">
+      <c r="G32" s="77" t="s">
         <v>71</v>
       </c>
     </row>

--- a/dataHQ_template.xlsx
+++ b/dataHQ_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e8f29e5c69611e4f/Jephin/CODEBOOK/dataHQ PH2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{ED923E39-6290-41D0-9134-F53FC29FCF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34F3F029-C531-4131-9D86-694AF489F486}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{ED923E39-6290-41D0-9134-F53FC29FCF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2B39F34-E9C7-4FF4-B83F-B463CA96D6AD}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{74DC5B4E-C759-4CAF-A571-81B2E018D03A}"/>
   </bookViews>
@@ -211,15 +211,9 @@
     <t>IS req</t>
   </si>
   <si>
-    <t>User Ad Failure Rate</t>
-  </si>
-  <si>
     <t>Impression Users</t>
   </si>
   <si>
-    <t>Ad Request Failure %</t>
-  </si>
-  <si>
     <t>User Ad Failure %</t>
   </si>
   <si>
@@ -266,6 +260,12 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>IS Request Failure %</t>
+  </si>
+  <si>
+    <t>IS User Ad Failure Rate</t>
   </si>
 </sst>
 </file>
@@ -1075,6 +1075,10 @@
 </file>
 
 <file path=xl/persons/person2.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person3.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -1452,7 +1456,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1461,7 +1465,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1470,7 +1474,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1479,7 +1483,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1569,7 +1573,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1578,7 +1582,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1587,7 +1591,7 @@
         <v>42</v>
       </c>
       <c r="C22" s="68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1596,7 +1600,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1616,7 +1620,7 @@
         <v>47</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1625,7 +1629,7 @@
         <v>49</v>
       </c>
       <c r="C26" s="73" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1651,7 +1655,7 @@
         <v>53</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C29" s="74">
         <v>0</v>
@@ -1660,7 +1664,7 @@
     <row r="30" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="78"/>
       <c r="B30" s="38" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C30" s="71">
         <v>0</v>
@@ -1668,10 +1672,10 @@
     </row>
     <row r="31" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="79" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C31" s="75">
         <v>0</v>
@@ -1680,7 +1684,7 @@
     <row r="32" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="79"/>
       <c r="B32" s="32" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C32" s="73">
         <v>0</v>
@@ -1689,7 +1693,7 @@
     <row r="33" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="79"/>
       <c r="B33" s="32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C33" s="73">
         <v>0</v>
@@ -1698,7 +1702,7 @@
     <row r="34" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="79"/>
       <c r="B34" s="32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C34" s="73">
         <v>0</v>
@@ -1707,7 +1711,7 @@
     <row r="35" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="79"/>
       <c r="B35" s="32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C35" s="73">
         <v>0</v>
@@ -1716,7 +1720,7 @@
     <row r="36" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="79"/>
       <c r="B36" s="32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C36" s="73">
         <v>0</v>
@@ -1725,14 +1729,14 @@
     <row r="37" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="79"/>
       <c r="B37" s="38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C37" s="76">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VzJycBoxLTH/vo8PkOVRWQ9S6/dmUnAWSea69WR+gbcvAiqp7FS3ywaYHNdY353HyZZ0r1zRRIHdSLIU+XjKAw==" saltValue="728X+bdZCY0buc0YLv2P2A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OaGBwAflO0sWChL4i9lUPIpYbqaAQweQLQ3KQuwdLBP/ZHQruz/Zw9cQ1wkEH4UKZhGOQh0QM1yjTtKk5tnWeQ==" saltValue="t3Wf0nraC/QcN4HbEh/ssA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="5">
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A37"/>
@@ -1813,7 +1817,7 @@
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1836,7 +1840,7 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1886,7 +1890,7 @@
       <c r="F8" s="84"/>
       <c r="G8" s="15"/>
       <c r="H8" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1906,7 +1910,7 @@
     <row r="10" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="53" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>7</v>
@@ -1968,7 +1972,7 @@
       <c r="D16" s="55"/>
       <c r="E16" s="56"/>
       <c r="F16" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G16" s="3"/>
     </row>
@@ -1980,7 +1984,7 @@
       <c r="D17" s="55"/>
       <c r="E17" s="56"/>
       <c r="F17" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1991,7 +1995,7 @@
       <c r="D18" s="59"/>
       <c r="E18" s="60"/>
       <c r="F18" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2038,7 +2042,7 @@
       <c r="E24" s="61"/>
       <c r="F24" s="62"/>
       <c r="G24" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2050,7 +2054,7 @@
       <c r="E25" s="63"/>
       <c r="F25" s="64"/>
       <c r="G25" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2062,7 +2066,7 @@
       <c r="E26" s="63"/>
       <c r="F26" s="64"/>
       <c r="G26" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2082,18 +2086,18 @@
     <row r="29" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="C29" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29" s="63"/>
       <c r="E29" s="63"/>
       <c r="F29" s="64"/>
       <c r="G29" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C30" s="44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D30" s="45" t="e">
         <f t="shared" ref="D30:F30" si="0">1-D29/D25</f>
@@ -2116,18 +2120,18 @@
     </row>
     <row r="32" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C32" s="39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D32" s="63"/>
       <c r="E32" s="63"/>
       <c r="F32" s="64"/>
       <c r="G32" s="77" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="3:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C33" s="44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D33" s="45" t="e">
         <f>1-D32/D26</f>
@@ -2150,7 +2154,7 @@
     </row>
     <row r="35" spans="3:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C35" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D35" s="48" t="e">
         <f>D32/D26</f>

--- a/dataHQ_template.xlsx
+++ b/dataHQ_template.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e8f29e5c69611e4f/Jephin/CODEBOOK/dataHQ PH2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{ED923E39-6290-41D0-9134-F53FC29FCF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2B39F34-E9C7-4FF4-B83F-B463CA96D6AD}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{ED923E39-6290-41D0-9134-F53FC29FCF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20679D5F-5184-4E9E-8243-6E4DC5931CD3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{74DC5B4E-C759-4CAF-A571-81B2E018D03A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
   <si>
     <t>India</t>
   </si>
@@ -251,9 +251,6 @@
   </si>
   <si>
     <t>(copy)</t>
-  </si>
-  <si>
-    <t>0 s</t>
   </si>
   <si>
     <t>editable</t>
@@ -341,6 +338,7 @@
       <sz val="11"/>
       <color rgb="FF632523"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1028,7 +1026,47 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{0DC3BE83-79DB-4048-973A-29B7D3FDDA66}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1379,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE862C0-5BE1-464B-94C2-A26A660F746C}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C37"/>
@@ -1456,7 +1494,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1465,7 +1503,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1474,7 +1512,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1483,7 +1521,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1573,7 +1611,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1582,7 +1620,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1591,7 +1629,7 @@
         <v>42</v>
       </c>
       <c r="C22" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1600,7 +1638,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1619,8 +1657,8 @@
       <c r="B25" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="72" t="s">
-        <v>68</v>
+      <c r="C25" s="72">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1628,8 +1666,8 @@
       <c r="B26" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="73" t="s">
-        <v>68</v>
+      <c r="C26" s="73">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1655,7 +1693,7 @@
         <v>53</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" s="74">
         <v>0</v>
@@ -1664,7 +1702,7 @@
     <row r="30" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="78"/>
       <c r="B30" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="71">
         <v>0</v>
@@ -1686,8 +1724,8 @@
       <c r="B32" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="73">
-        <v>0</v>
+      <c r="C32" s="73" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1695,8 +1733,8 @@
       <c r="B33" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="73">
-        <v>0</v>
+      <c r="C33" s="73" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1704,8 +1742,8 @@
       <c r="B34" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="73">
-        <v>0</v>
+      <c r="C34" s="73" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1713,8 +1751,8 @@
       <c r="B35" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="73">
-        <v>0</v>
+      <c r="C35" s="73" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1722,8 +1760,8 @@
       <c r="B36" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="73">
-        <v>0</v>
+      <c r="C36" s="73" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1731,8 +1769,8 @@
       <c r="B37" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="76">
-        <v>0</v>
+      <c r="C37" s="76" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1751,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E109469C-7A8D-45F8-84D9-5598B4A88989}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:H37"/>
@@ -1817,7 +1855,7 @@
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1840,7 +1878,7 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1890,7 +1928,7 @@
       <c r="F8" s="84"/>
       <c r="G8" s="15"/>
       <c r="H8" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1915,8 +1953,7 @@
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21" t="e">
+      <c r="D10" s="21" t="e">
         <f>D7/D8</f>
         <v>#DIV/0!</v>
       </c>
@@ -1972,7 +2009,7 @@
       <c r="D16" s="55"/>
       <c r="E16" s="56"/>
       <c r="F16" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3"/>
     </row>
@@ -1984,7 +2021,7 @@
       <c r="D17" s="55"/>
       <c r="E17" s="56"/>
       <c r="F17" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1995,7 +2032,7 @@
       <c r="D18" s="59"/>
       <c r="E18" s="60"/>
       <c r="F18" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2042,7 +2079,7 @@
       <c r="E24" s="61"/>
       <c r="F24" s="62"/>
       <c r="G24" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2054,7 +2091,7 @@
       <c r="E25" s="63"/>
       <c r="F25" s="64"/>
       <c r="G25" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2066,7 +2103,7 @@
       <c r="E26" s="63"/>
       <c r="F26" s="64"/>
       <c r="G26" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2092,7 +2129,7 @@
       <c r="E29" s="63"/>
       <c r="F29" s="64"/>
       <c r="G29" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2126,7 +2163,7 @@
       <c r="E32" s="63"/>
       <c r="F32" s="64"/>
       <c r="G32" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="3:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2177,14 +2214,13 @@
     </row>
     <row r="37" spans="3:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="4v1/eWWl8jp07y2twgXHUdD9QUW/dRI3YoLiDRgHOQ4Z9IA1XK+LTF+21zBqZQp3dkkGIjLItBZLFetFWhQkwQ==" saltValue="muCu1LbOl5wo67Og6Mei0g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="4">
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="C21:C22"/>
   </mergeCells>
-  <conditionalFormatting sqref="D10:F10">
+  <conditionalFormatting sqref="D10">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
